--- a/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-ext-patient-religion.xlsx
+++ b/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-ext-patient-religion.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-patient-religion</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-patient-religion</t>
   </si>
   <si>
     <t>Version</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:16:57+00:00</t>
+    <t>2026-10-13T08:41:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>HL7® Austria FHIR® Core Extension for the religion (registered in Austria) of a patient.
+    <t>**DEPRECATED** HL7® Austria FHIR® Core Extension for the religion (registered in Austria) of a patient.
 The extension is used to encode the religious confession of a patient (only confessions registered in Austria). Furthermore, it uses the official [HL7 AT CodeSystem](https://termpub.gesundheit.gv.at:443/TermBrowser/gui/main/main.zul?loadType=CodeSystem&amp;loadName=HL7 AT ReligionAustria) for religion and is therefore aligned with the ELGA ValueSet, respectively.</t>
   </si>
   <si>
@@ -136,7 +136,7 @@
     <t>element:Patient</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient#Patient</t>
+    <t>element:https://fhir.hl7.at/core/r5/StructureDefinition/at-core-patient#Patient</t>
   </si>
   <si>
     <t>ID</t>
